--- a/data/output/output_data.xlsx
+++ b/data/output/output_data.xlsx
@@ -92,7 +92,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -317,6 +317,7 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
     <border/>
     <border/>
   </borders>
@@ -325,7 +326,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -498,6 +499,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1268,14 +1273,14 @@
       <c r="C14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="66" t="inlineStr">
+      <c r="A15" s="68" t="inlineStr">
         <is>
           <t>Премия РП</t>
         </is>
       </c>
       <c r="B15" s="1" t="n"/>
       <c r="C15" s="1" t="n"/>
-      <c r="I15" s="67" t="n">
+      <c r="I15" s="69" t="n">
         <v>14166</v>
       </c>
     </row>
